--- a/assets/files/atelier/synthese_fabien_chevalier.xlsx
+++ b/assets/files/atelier/synthese_fabien_chevalier.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabien/Documents/GitHub/fabienchevalier.github.io/assets/files/atelier/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UTILISATEURS\fch\Desktop\BTS - Local\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C2D0C74-A0A3-B04F-BABF-807470B8DD7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B354BFC-300D-404D-91F5-20CA1641CFE7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="33600" windowHeight="19575" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
@@ -127,10 +127,6 @@
     <t>Audit d'un système d'information et identifications des besoins du client</t>
   </si>
   <si>
-    <t xml:space="preserve">Réalisation d'une infrastructure TOIP
-</t>
-  </si>
-  <si>
     <t>Aide à l'optimisation du SEO web de l'entreprise</t>
   </si>
   <si>
@@ -286,16 +282,20 @@
     <t>Déploiement  d'un serveur LDAP Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">Mise en place de l'infrastructure pour le passage de l'épreuve E5
-</t>
-  </si>
-  <si>
     <t>13/01/2022
 au 
 10/05/2022</t>
   </si>
   <si>
     <t>Installation de GLPI et du plugin Fusion-Inventory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réalisation d'une infrastructure TOIP avec PacketTracer
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mise en place d'un serveur LAMP conteneurisé avec Docker
+</t>
   </si>
 </sst>
 </file>
@@ -871,9 +871,45 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -891,42 +927,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1271,66 +1271,66 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AQ82"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="70.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="1" customWidth="1"/>
-    <col min="3" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="43" width="11.5" customWidth="1"/>
-    <col min="44" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="1" width="70.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" style="1" customWidth="1"/>
+    <col min="3" max="8" width="18.7109375" style="1" customWidth="1"/>
+    <col min="9" max="43" width="11.42578125" customWidth="1"/>
+    <col min="44" max="16384" width="10.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="35" t="s">
+    <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35" t="s">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="35"/>
-    </row>
-    <row r="2" spans="1:43" ht="41" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="35" t="s">
+      <c r="H1" s="38"/>
+    </row>
+    <row r="2" spans="1:43" ht="41.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-    </row>
-    <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="36" t="s">
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+    </row>
+    <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="41"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="52"/>
+      <c r="H3" s="53"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="36" t="s">
+    <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
       <c r="F4" s="20" t="s">
         <v>8</v>
       </c>
@@ -1341,11 +1341,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="42" t="s">
+    <row r="5" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="46" t="s">
         <v>18</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -1367,9 +1367,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="43"/>
-      <c r="B6" s="51"/>
+    <row r="6" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="37"/>
+      <c r="B6" s="47"/>
       <c r="C6" s="28" t="s">
         <v>9</v>
       </c>
@@ -1424,17 +1424,17 @@
       <c r="AP6"/>
       <c r="AQ6"/>
     </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A7" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="46"/>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A7" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="41"/>
       <c r="I7"/>
       <c r="J7"/>
       <c r="K7"/>
@@ -1471,12 +1471,12 @@
       <c r="AP7"/>
       <c r="AQ7"/>
     </row>
-    <row r="8" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>24</v>
@@ -1524,12 +1524,12 @@
       <c r="AP8"/>
       <c r="AQ8"/>
     </row>
-    <row r="9" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" s="12"/>
       <c r="D9" s="12" t="s">
@@ -1577,12 +1577,12 @@
       <c r="AP9"/>
       <c r="AQ9"/>
     </row>
-    <row r="10" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12" t="s">
@@ -1630,12 +1630,12 @@
       <c r="AP10"/>
       <c r="AQ10"/>
     </row>
-    <row r="11" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -1685,12 +1685,12 @@
       <c r="AP11"/>
       <c r="AQ11"/>
     </row>
-    <row r="12" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="13"/>
@@ -1736,12 +1736,12 @@
       <c r="AP12"/>
       <c r="AQ12"/>
     </row>
-    <row r="13" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>24</v>
@@ -1789,12 +1789,12 @@
       <c r="AP13"/>
       <c r="AQ13"/>
     </row>
-    <row r="14" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>24</v>
@@ -1842,12 +1842,12 @@
       <c r="AP14"/>
       <c r="AQ14"/>
     </row>
-    <row r="15" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="26" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>24</v>
@@ -1897,12 +1897,12 @@
       <c r="AP15"/>
       <c r="AQ15"/>
     </row>
-    <row r="16" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>24</v>
@@ -1948,12 +1948,12 @@
       <c r="AP16"/>
       <c r="AQ16"/>
     </row>
-    <row r="17" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17" s="52" t="s">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>67</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -1999,17 +1999,17 @@
       <c r="AP17"/>
       <c r="AQ17"/>
     </row>
-    <row r="18" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A18" s="53" t="s">
+    <row r="18" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A18" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="48"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="49"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="44"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -2046,12 +2046,12 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>25</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="12" t="s">
@@ -2097,12 +2097,12 @@
       <c r="AP19"/>
       <c r="AQ19"/>
     </row>
-    <row r="20" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>26</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>24</v>
@@ -2152,12 +2152,12 @@
       <c r="AP20"/>
       <c r="AQ20"/>
     </row>
-    <row r="21" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>24</v>
@@ -2209,12 +2209,12 @@
       <c r="AP21"/>
       <c r="AQ21"/>
     </row>
-    <row r="22" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>24</v>
@@ -2266,12 +2266,12 @@
       <c r="AP22"/>
       <c r="AQ22"/>
     </row>
-    <row r="23" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="13"/>
@@ -2317,12 +2317,12 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>24</v>
@@ -2370,12 +2370,12 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>24</v>
@@ -2423,12 +2423,12 @@
       <c r="AP25"/>
       <c r="AQ25"/>
     </row>
-    <row r="26" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B26" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>24</v>
@@ -2474,17 +2474,17 @@
       <c r="AP26"/>
       <c r="AQ26"/>
     </row>
-    <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A27" s="47" t="s">
+    <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A27" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="48"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="48"/>
-      <c r="H27" s="49"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="44"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2521,12 +2521,12 @@
       <c r="AP27"/>
       <c r="AQ27"/>
     </row>
-    <row r="28" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
         <v>27</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>24</v>
@@ -2574,12 +2574,12 @@
       <c r="AP28"/>
       <c r="AQ28"/>
     </row>
-    <row r="29" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>24</v>
@@ -2627,12 +2627,12 @@
       <c r="AP29"/>
       <c r="AQ29"/>
     </row>
-    <row r="30" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
@@ -2678,12 +2678,12 @@
       <c r="AP30"/>
       <c r="AQ30"/>
     </row>
-    <row r="31" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C31" s="13"/>
       <c r="D31" s="12" t="s">
@@ -2731,12 +2731,12 @@
       <c r="AP31"/>
       <c r="AQ31"/>
     </row>
-    <row r="32" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C32" s="13"/>
       <c r="D32" s="12" t="s">
@@ -2784,12 +2784,12 @@
       <c r="AP32"/>
       <c r="AQ32"/>
     </row>
-    <row r="33" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B33" s="32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C33" s="15"/>
       <c r="D33" s="12" t="s">
@@ -2837,12 +2837,12 @@
       <c r="AP33"/>
       <c r="AQ33"/>
     </row>
-    <row r="34" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C34" s="15"/>
       <c r="D34" s="12" t="s">
@@ -2890,12 +2890,12 @@
       <c r="AP34"/>
       <c r="AQ34"/>
     </row>
-    <row r="35" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
@@ -2941,7 +2941,7 @@
       <c r="AP35"/>
       <c r="AQ35"/>
     </row>
-    <row r="36" spans="1:43" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:43" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="5"/>
       <c r="B36" s="3"/>
       <c r="C36" s="4"/>
@@ -2986,65 +2986,65 @@
       <c r="AP36"/>
       <c r="AQ36"/>
     </row>
-    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="49" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="50" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="51" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="52" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="53" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="54" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="55" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="56" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="57" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="58" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="59" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="60" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="61" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="62" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="63" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="64" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="65" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="66" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="67" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="68" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="69" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="70" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="71" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="72" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="73" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="74" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="75" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="76" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="77" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="78" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="79" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="80" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="81" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="82" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="49" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="50" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="51" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="52" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="54" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="55" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="56" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="57" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="58" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="59" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="60" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="61" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="62" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="63" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="64" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="65" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="66" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="68" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="69" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="70" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="71" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="72" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="73" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="74" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="75" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="76" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="77" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="78" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="79" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="80" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="81" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="82" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/assets/files/atelier/synthese_fabien_chevalier.xlsx
+++ b/assets/files/atelier/synthese_fabien_chevalier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UTILISATEURS\fch\Desktop\BTS - Local\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B354BFC-300D-404D-91F5-20CA1641CFE7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BE54B2-DC16-4FA9-8D20-75266535B891}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="495" windowWidth="33600" windowHeight="19575" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -290,11 +290,11 @@
     <t>Installation de GLPI et du plugin Fusion-Inventory</t>
   </si>
   <si>
-    <t xml:space="preserve">Réalisation d'une infrastructure TOIP avec PacketTracer
+    <t xml:space="preserve">Mise en place d'un serveur LAMP conteneurisé avec Docker
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Mise en place d'un serveur LAMP conteneurisé avec Docker
+    <t xml:space="preserve">Réalisation d'une infrastructure intégrant la VOIP avec PacketTracer
 </t>
   </si>
 </sst>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B15" s="31" t="s">
         <v>49</v>
@@ -1950,7 +1950,7 @@
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B17" s="35" t="s">
         <v>67</v>
